--- a/mercadolivre.xlsx
+++ b/mercadolivre.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -426,6 +426,12 @@
       <c r="F1" t="str">
         <v>Badge</v>
       </c>
+      <c r="G1" t="str">
+        <v>Imagem</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Preco</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -446,10 +452,16 @@
       <c r="F2" t="str">
         <v>Frete Grátis</v>
       </c>
+      <c r="G2" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a9/MercadoLivre.svg/256px-MercadoLivre.svg.png</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Ver Oferta</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/mercadolivre.xlsx
+++ b/mercadolivre.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Links" sheetId="1" r:id="rId1"/>
+    <sheet name="Produtos" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,15 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
-  <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="50.83203125" customWidth="1"/>
-    <col min="3" max="3" width="40.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:H71"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -435,33 +427,1827 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Smartphone Xiaomi Redmi Note 13</v>
+        <v>Máquina De Solda Multiprocesso Mig Flex 150a Pró Euro Bivolt Mig Sem Gás Mma Tig Laranja/preto 127/220v</v>
       </c>
       <c r="B2" t="str">
-        <v>128GB, Câmera 108MP, Bateria 5000mAh</v>
+        <v>Oferta Mercado Livre</v>
       </c>
       <c r="C2" t="str">
-        <v>https://mercadolivre.com.br</v>
+        <v>https://meli.la/1Wa1bjd</v>
       </c>
       <c r="D2" t="str">
-        <v>smartphone</v>
+        <v>shopping-cart</v>
       </c>
       <c r="E2" t="str">
         <v>#ffe600</v>
       </c>
       <c r="F2" t="str">
-        <v>Frete Grátis</v>
+        <v>Mercado Livre</v>
       </c>
       <c r="G2" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a9/MercadoLivre.svg/256px-MercadoLivre.svg.png</v>
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_790599-MLA108486991448_032026-V.webp</v>
       </c>
       <c r="H2" t="str">
-        <v>Ver Oferta</v>
+        <v>R$ 598</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Macaco Hidráulico Garrafa 20 Toneladas 2218 Bremen</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://meli.la/2DmKYYo</v>
+      </c>
+      <c r="D3" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E3" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G3" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_732459-MLA99440354688_112025-V.webp</v>
+      </c>
+      <c r="H3" t="str">
+        <v>R$ 226</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Secador De Cabelos Philco psc3500 4 Em 1 dobrável motor bldc Prateado Bege 220v</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C4" t="str">
+        <v>https://meli.la/1oVMZ8P</v>
+      </c>
+      <c r="D4" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E4" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G4" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_720624-MLA99531483484_122025-V.webp</v>
+      </c>
+      <c r="H4" t="str">
+        <v>R$ 421</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Caixa De Som Bluetooth Amplificada Grande Potencia Hz-2000 + 2 Microfones Sem Fio Limpo Preto 127/220v</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C5" t="str">
+        <v>https://meli.la/2P4WVgF</v>
+      </c>
+      <c r="D5" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E5" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G5" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_852584-MLA96893578680_112025-V.webp</v>
+      </c>
+      <c r="H5" t="str">
+        <v>R$ 669</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Body Splash Arabe C/4un 200ml Perfume Masculino De Luxo</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C6" t="str">
+        <v>https://meli.la/1dETnDw</v>
+      </c>
+      <c r="D6" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E6" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G6" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_732841-MLA108876170355_032026-V.webp</v>
+      </c>
+      <c r="H6" t="str">
+        <v>R$ 75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Kit 6 Pares Meias Lupo Cano Médio Esportivas Academia</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C7" t="str">
+        <v>https://meli.la/2SHLmv1</v>
+      </c>
+      <c r="D7" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E7" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G7" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_906724-MLB75371075175_032024-V-kit-6-pares-meias-lupo-cano-medio-esportivas-academia.webp</v>
+      </c>
+      <c r="H7" t="str">
+        <v>R$ 45</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Cadeira Escritório Presidente Ergonômica Arcanis Preto Marqs Home Com Suporte Apoio Lombar Tecido Mesh Premium Resistente Profissional Regulagem Ajuste De Altura Malha</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C8" t="str">
+        <v>https://meli.la/1pP8K8y</v>
+      </c>
+      <c r="D8" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E8" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G8" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_892750-MLA110183247129_042026-V.webp</v>
+      </c>
+      <c r="H8" t="str">
+        <v>R$ 459</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Kit Reparo Caixa Acoplada Completo Mecanismo Universal</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C9" t="str">
+        <v>https://meli.la/1NohVL4</v>
+      </c>
+      <c r="D9" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E9" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G9" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_930662-MLA99627272872_122025-V.webp</v>
+      </c>
+      <c r="H9" t="str">
+        <v>R$ 42</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Tênis Fila Rise Up Masculino Confortável Mesh Leve Esportivo</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C10" t="str">
+        <v>https://meli.la/176b4QS</v>
+      </c>
+      <c r="D10" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E10" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G10" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_933337-MLB107686888084_032026-V-tnis-fila-rise-up-masculino-confortavel-mesh-leve-esportivo.webp</v>
+      </c>
+      <c r="H10" t="str">
+        <v>R$ 199</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Calça Jeans Masculina Tradicional Corte Reto</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C11" t="str">
+        <v>https://meli.la/1oE9CzP</v>
+      </c>
+      <c r="D11" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E11" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G11" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_996599-MLB88495135003_072025-V-calca-jeans-masculina-tradicional-corte-reto.webp</v>
+      </c>
+      <c r="H11" t="str">
+        <v>R$ 57</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Kit 3x Perfumes Colônia Miniatura Cebolinha Turma Da Mônica Jequiti De 25ml</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C12" t="str">
+        <v>https://meli.la/2emp7J3</v>
+      </c>
+      <c r="D12" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E12" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G12" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_855393-MLA109559501011_032026-V.webp</v>
+      </c>
+      <c r="H12" t="str">
+        <v>R$ 60</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Carregador Compativel Com iPhone 8 X Xr 11 12 13 14 Pro Max Turbo Fonte Tipo C Boyu Cell Branco</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C13" t="str">
+        <v>https://meli.la/2NjDzxJ</v>
+      </c>
+      <c r="D13" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E13" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G13" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_945381-MLA108251647129_032026-V.webp</v>
+      </c>
+      <c r="H13" t="str">
+        <v>R$ 28</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Armário Aéreo De Cozinha Cor Branco 3 Portas Rose Itatiaia</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C14" t="str">
+        <v>https://meli.la/24UaMYK</v>
+      </c>
+      <c r="D14" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E14" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G14" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_977816-MLA95708433834_102025-V.webp</v>
+      </c>
+      <c r="H14" t="str">
+        <v>R$ 199</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Conjunto Suplex Blackout Zero Transparência Legging E Croppe</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C15" t="str">
+        <v>https://meli.la/2ohEuoN</v>
+      </c>
+      <c r="D15" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E15" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G15" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_671881-MLB98917836900_112025-V-conjunto-suplex-blackout-zero-transparncia-legging-e-croppe.webp</v>
+      </c>
+      <c r="H15" t="str">
+        <v>R$ 67</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Calça Cargo Feminina Wide Leg Cintura Alta Jeans Stillger</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C16" t="str">
+        <v>https://meli.la/2cSpk8m</v>
+      </c>
+      <c r="D16" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E16" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G16" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_727067-MLB110787686755_042026-V-calca-cargo-feminina-wide-leg-cintura-alta-jeans-stillger.webp</v>
+      </c>
+      <c r="H16" t="str">
+        <v>R$ 69</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Kit 3 Camisetas Térmicas Masculina Segunda Pele Camisa Uv50-</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C17" t="str">
+        <v>https://meli.la/2hwtqFe</v>
+      </c>
+      <c r="D17" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E17" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G17" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_972766-MLB109277690414_042026-V-kit-3-camisetas-termicas-masculina-segunda-pele-camisa-uv50-.webp</v>
+      </c>
+      <c r="H17" t="str">
+        <v>R$ 73</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Cortina 3,00x2,80 Metros Blackout Blecaute Gelo Corta Luz Em Tecido Grosso Para Quarto E Sala Casa Laura Enxovais</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C18" t="str">
+        <v>https://meli.la/23hQ94f</v>
+      </c>
+      <c r="D18" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E18" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G18" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_765831-MLA99416628534_112025-V.webp</v>
+      </c>
+      <c r="H18" t="str">
+        <v>R$ 75</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Short Duplo Compreensão Fitness Bermuda Academia Feminino</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C19" t="str">
+        <v>https://meli.la/25Qi2Mv</v>
+      </c>
+      <c r="D19" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E19" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G19" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_615145-MLB90274630198_082025-V-short-duplo-compreenso-fitness-bermuda-academia-feminino.webp</v>
+      </c>
+      <c r="H19" t="str">
+        <v>R$ 38</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Kit 3 Camisetas Algodão Dia Dia Sandrini Básica Conforto</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C20" t="str">
+        <v>https://meli.la/1rPyEzh</v>
+      </c>
+      <c r="D20" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E20" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G20" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_683225-MLB100382923917_122025-V-kit-3-camisetas-algodo-dia-dia-sandrini-basica-conforto.webp</v>
+      </c>
+      <c r="H20" t="str">
+        <v>R$ 59</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Esmerilhadeira Lixadeira Angular Profissional Arstheco 850w 115mm 12.000rpm Cor Amarelo Com Acessório Compacta Eficiente Frequência 60hz 220v 50hz/60hz</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C21" t="str">
+        <v>https://meli.la/14FUEmL</v>
+      </c>
+      <c r="D21" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E21" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G21" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_813021-MLA109434722042_042026-V.webp</v>
+      </c>
+      <c r="H21" t="str">
+        <v>R$ 107</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Kit 15 Pares Meias Sport Algodão Cano Alto Sandrini Conforto Sortidos 39-43</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C22" t="str">
+        <v>https://meli.la/1emgAiH</v>
+      </c>
+      <c r="D22" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E22" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G22" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_628716-MLB78359677743_082024-V.webp</v>
+      </c>
+      <c r="H22" t="str">
+        <v>R$ 59</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Kit 6 Pares Meias Soquete Invisível Lupo Algodão Unissex</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C23" t="str">
+        <v>https://meli.la/2MJdmce</v>
+      </c>
+      <c r="D23" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E23" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G23" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_756748-MLB79675885161_092024-V-kit-6-pares-meias-soquete-invisivel-lupo-algodo-unissex.webp</v>
+      </c>
+      <c r="H23" t="str">
+        <v>R$ 48</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Calça Plus Size Jeans Feminina Wide Leg Levanta Bumbum</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C24" t="str">
+        <v>https://meli.la/27vsGDt</v>
+      </c>
+      <c r="D24" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E24" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G24" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_984316-MLB106453844662_022026-V-calca-plus-size-jeans-feminina-wide-leg-levanta-bumbum.webp</v>
+      </c>
+      <c r="H24" t="str">
+        <v>R$ 71</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Máquina De Corte Acabamento Profissional Com Aparador Cabelo Pelo Barbear Maquininha Detalhes Sem Fio Preto 127/220v</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C25" t="str">
+        <v>https://meli.la/1uYuVq8</v>
+      </c>
+      <c r="D25" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E25" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G25" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_620356-MLA95678651850_102025-V.webp</v>
+      </c>
+      <c r="H25" t="str">
+        <v>R$ 53</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Kit 2 Cobertor Mantinha Microfibra Casal Manta Macia Diversas Cores Lisa Sortida Liso 700 G</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C26" t="str">
+        <v>https://meli.la/2uhoG7D</v>
+      </c>
+      <c r="D26" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E26" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G26" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_802073-MLA100073102841_122025-V.webp</v>
+      </c>
+      <c r="H26" t="str">
+        <v>R$ 43</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Creme Hidratante Facial Principia Ch-01 Karité Glicerina 50g Todo Tipo De Pele Dia/noite</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C27" t="str">
+        <v>https://meli.la/2GUQFcL</v>
+      </c>
+      <c r="D27" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E27" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G27" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_918525-MLA102373426972_122025-V.webp</v>
+      </c>
+      <c r="H27" t="str">
+        <v>R$ 39</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Cortina 3,00x2,50 Metros Blackout Blecaute Gelo Corta Luz Em Tecido Grosso Para Quarto E Sala Casa Laura Enxovais</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C28" t="str">
+        <v>https://meli.la/1JLqEac</v>
+      </c>
+      <c r="D28" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E28" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G28" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_727827-MLA99486610642_112025-V.webp</v>
+      </c>
+      <c r="H28" t="str">
+        <v>R$ 75</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Carregador Compativel Com Samsung Galaxy S25 S24 S23 S21 S20 Fe Plus Motorola M22 M31 M32 M62 M63 M64 G15 Xiaomi Redmi Note 12 13 14 15 LG Cor Preto Turbo Super Rápido Fonte Tipo C Boyu Cell</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C29" t="str">
+        <v>https://meli.la/2vb8Zbh</v>
+      </c>
+      <c r="D29" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E29" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G29" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_785588-MLA110035769234_042026-V.webp</v>
+      </c>
+      <c r="H29" t="str">
+        <v>R$ 36</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Itatiaia Rose Trp 1,05 Balcão 3 Portas 1 Gaveta Com Tampo Cor Preto</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C30" t="str">
+        <v>https://meli.la/2xh9Yz5</v>
+      </c>
+      <c r="D30" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E30" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G30" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_720721-MLA99981430557_112025-V.webp</v>
+      </c>
+      <c r="H30" t="str">
+        <v>R$ 384</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Kit Desengripante Spray 300ml 12 Unidades Te0001161 Lub Fast</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C31" t="str">
+        <v>https://meli.la/1tThdPU</v>
+      </c>
+      <c r="D31" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E31" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G31" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_664912-MLA99926030929_112025-V.webp</v>
+      </c>
+      <c r="H31" t="str">
+        <v>R$ 71</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Sutiã Nayane Rodrigues Tomara Que Caia Bojo Feminino</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C32" t="str">
+        <v>https://meli.la/1iRrLm2</v>
+      </c>
+      <c r="D32" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E32" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G32" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_919530-MLB87080753170_072025-V-suti-nayane-rodrigues-tomara-que-caia-bojo-feminino.webp</v>
+      </c>
+      <c r="H32" t="str">
+        <v>R$ 62</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Top Puma Academia Fitness Original Nadador Alta Sustentação</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C33" t="str">
+        <v>https://meli.la/1yJ37XN</v>
+      </c>
+      <c r="D33" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E33" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G33" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_983763-MLB87025106336_072025-V-top-puma-academia-fitness-original-nadador-alta-sustentaco.webp</v>
+      </c>
+      <c r="H33" t="str">
+        <v>R$ 44</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Relogio Smartwatch Mulher Inteligente Feminino Esportivo Chamadas Bluetooth Rose Milanês Rosa</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C34" t="str">
+        <v>https://meli.la/299u7z5</v>
+      </c>
+      <c r="D34" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E34" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G34" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_804998-MLA109634721551_032026-V.webp</v>
+      </c>
+      <c r="H34" t="str">
+        <v>R$ 178</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Tapete 2,00x1,50 Peludo Felpudo Para Sala E Quarto Cores Cor Bege-mesclado Desenho Do Tecido Pelo Alto Casa Laura... 2 M 1.5 M</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C35" t="str">
+        <v>https://meli.la/1e8g94x</v>
+      </c>
+      <c r="D35" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E35" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G35" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_755662-MLA99498152944_112025-V.webp</v>
+      </c>
+      <c r="H35" t="str">
+        <v>R$ 62</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Kit 3 Espuma Expansiva Pu Multiuso Vedação Selante Isolante</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C36" t="str">
+        <v>https://meli.la/1bbb5iA</v>
+      </c>
+      <c r="D36" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E36" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G36" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_979521-MLB98932451840_112025-V.webp</v>
+      </c>
+      <c r="H36" t="str">
+        <v>R$ 55</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Passadeira Felpuda Bege Corredor 2m Texfine Poliéster Sala Quarto Cozinha 2 M 60 Cm</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C37" t="str">
+        <v>https://meli.la/16kPui9</v>
+      </c>
+      <c r="D37" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E37" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G37" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_730153-MLA100075937625_122025-V.webp</v>
+      </c>
+      <c r="H37" t="str">
+        <v>R$ 38</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Kit 2 Microfone Celular De Lapela Sem Fio Duplo Android iPhone Redução De Ruído Mega Digital Eletrônicos Preto</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C38" t="str">
+        <v>https://meli.la/1PpHWFb</v>
+      </c>
+      <c r="D38" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E38" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G38" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_713779-MLA109874215301_032026-V.webp</v>
+      </c>
+      <c r="H38" t="str">
+        <v>R$ 123</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Cesto Para Roupas Bambu Dobrável Com Tampa Bege 60l Texfine Bege Retangular Liso</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C39" t="str">
+        <v>https://meli.la/33aG5qk</v>
+      </c>
+      <c r="D39" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E39" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G39" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_850430-MLA95526781368_102025-V.webp</v>
+      </c>
+      <c r="H39" t="str">
+        <v>R$ 61</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Kit 2 Refletor Led Holofote Slim 300w Prova D'água Cor Da Luz Branco Frio 127/220v Preto</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C40" t="str">
+        <v>https://meli.la/23U5Yq5</v>
+      </c>
+      <c r="D40" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E40" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G40" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_962708-MLA110741965535_042026-V.webp</v>
+      </c>
+      <c r="H40" t="str">
+        <v>R$ 39</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Calça Jeans Plus Size Feminina Skinny Com Lycra Cintura Alta</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C41" t="str">
+        <v>https://meli.la/1Hq6kiZ</v>
+      </c>
+      <c r="D41" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E41" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G41" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_644303-MLB106351065029_022026-V-calca-jeans-plus-size-feminina-skinny-com-lycra-cintura-alta.webp</v>
+      </c>
+      <c r="H41" t="str">
+        <v>R$ 59</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2x3m - 4x6m Tela Sombreamento Toldo Sombrite Proteção 90% Cáqui-4x6</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C42" t="str">
+        <v>https://meli.la/27AE5hR</v>
+      </c>
+      <c r="D42" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E42" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G42" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_746489-MLB94953181650_102025-V.webp</v>
+      </c>
+      <c r="H42" t="str">
+        <v>R$ 151</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Henna Menela Castanho Médio Padrão Profissional Para Designer De Sobrancelhas 2.5g Com Fixador E Nanotecnologia Completo</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C43" t="str">
+        <v>https://meli.la/2rxxAhw</v>
+      </c>
+      <c r="D43" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E43" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G43" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_632117-MLA100968109364_122025-V.webp</v>
+      </c>
+      <c r="H43" t="str">
+        <v>R$ 54</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Capa Protetor De Colchão Elástico Queen Impermeável Casa Laura Enxovais Matelado Cor Branco</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C44" t="str">
+        <v>https://meli.la/19HEksr</v>
+      </c>
+      <c r="D44" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E44" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G44" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_940147-MLA100067586777_122025-V.webp</v>
+      </c>
+      <c r="H44" t="str">
+        <v>R$ 29</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Kit 2 Microfone Sem Fio Profissional Bluetooth Led Com Receptor Para Karaoke Igreja, Palestra</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C45" t="str">
+        <v>https://meli.la/1oy6xJC</v>
+      </c>
+      <c r="D45" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E45" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G45" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_604834-MLA99524340116_122025-V.webp</v>
+      </c>
+      <c r="H45" t="str">
+        <v>R$ 119</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Jogo De Lençol Queen 3 Peças 400 Fios Com Elástico Hotel Preto Liso</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C46" t="str">
+        <v>https://meli.la/2rRBbip</v>
+      </c>
+      <c r="D46" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E46" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G46" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_839175-MLA104656353597_012026-V.webp</v>
+      </c>
+      <c r="H46" t="str">
+        <v>R$ 31</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Mochila Tática Impermeável Militar Reforçada Grande 50 Litros Masculina Feminina Anne Cáqui Areia Marrom Liso</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C47" t="str">
+        <v>https://meli.la/1iQPYvt</v>
+      </c>
+      <c r="D47" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E47" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G47" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_622805-MLA99625620414_122025-V.webp</v>
+      </c>
+      <c r="H47" t="str">
+        <v>R$ 119</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Teste De Circuito Elétrico Automotivo Medidor Fusível 6-24v 6v 12v 24v</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C48" t="str">
+        <v>https://meli.la/1VnDgee</v>
+      </c>
+      <c r="D48" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E48" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G48" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_672497-MLB100720230835_122025-V.webp</v>
+      </c>
+      <c r="H48" t="str">
+        <v>R$ 28</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Espelho Adnet De Parede Escandinavo 60cm Com Suporte Cor Preto - Ideal Como Espelho Para Banheiro, Sala Ou Quarto. Redondo E Grande, Perfeito Para Penteadeira E Maquiagem</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C49" t="str">
+        <v>https://meli.la/2rRBfym</v>
+      </c>
+      <c r="D49" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E49" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G49" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_875651-MLA106644312415_022026-V.webp</v>
+      </c>
+      <c r="H49" t="str">
+        <v>R$ 67</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Jogo De Toalha Banho 4 Peças 100 Algodão 400 Gr/m Loft Camesa Chumbo Liso</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C50" t="str">
+        <v>https://meli.la/1BJw7Xp</v>
+      </c>
+      <c r="D50" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E50" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G50" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_799726-MLA96094691621_102025-V.webp</v>
+      </c>
+      <c r="H50" t="str">
+        <v>R$ 110</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Concertina Cerca 30 Cm 40 Metros + Kit De Instalação - Cod 5</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C51" t="str">
+        <v>https://meli.la/2Rs1LJT</v>
+      </c>
+      <c r="D51" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E51" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G51" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_843389-MLB31361295166_072019-V.webp</v>
+      </c>
+      <c r="H51" t="str">
+        <v>R$ 351</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Espelho Redondo 50cm C/ Led Para Parede Quarto Banheiro Sala Moldura Redondo 50cm Led Quente</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C52" t="str">
+        <v>https://meli.la/2uJh85N</v>
+      </c>
+      <c r="D52" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E52" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G52" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_666299-MLA98073521492_112025-V.webp</v>
+      </c>
+      <c r="H52" t="str">
+        <v>R$ 69</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Pomada Em Pó Para Cabelos Baboon 15g</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C53" t="str">
+        <v>https://meli.la/29FnvNS</v>
+      </c>
+      <c r="D53" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E53" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G53" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_989943-MLB50135997133_052022-V.webp</v>
+      </c>
+      <c r="H53" t="str">
+        <v>R$ 87</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Chuveiro Ducha Loren Shower Eletrônico Lorenzetti 220v 7500w Branco 220v 7.5 Kw</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C54" t="str">
+        <v>https://meli.la/1eEjUbk</v>
+      </c>
+      <c r="D54" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E54" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G54" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_681773-MLB110654532083_042026-V.webp</v>
+      </c>
+      <c r="H54" t="str">
+        <v>R$ 158</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Kit Borrachas Vedação 4 Portas Fiesta Hatch Sedan 02 Até 13</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C55" t="str">
+        <v>https://meli.la/2K6LktJ</v>
+      </c>
+      <c r="D55" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E55" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G55" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_964470-MLB74931966811_032024-V.webp</v>
+      </c>
+      <c r="H55" t="str">
+        <v>R$ 187</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Kit 4 Regatas Plus Size Fitness Academia Gg - G1 - G2 - G3</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C56" t="str">
+        <v>https://meli.la/2tEVhfo</v>
+      </c>
+      <c r="D56" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E56" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G56" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_901734-MLB69548812414_052023-V-kit-4-regatas-plus-size-fitness-academia-gg-g1-g2-g3.webp</v>
+      </c>
+      <c r="H56" t="str">
+        <v>R$ 78</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Scanner Carro Automotivo Bluetooth Obd2 V2.1 Android Veiculo</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C57" t="str">
+        <v xml:space="preserve">https://meli.la/1M9spaC </v>
+      </c>
+      <c r="D57" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E57" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G57" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_672238-MLB84517884394_052025-V.webp</v>
+      </c>
+      <c r="H57" t="str">
+        <v>R$ 25</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Relógio Masculino De Pulso Social Clássico Casual Original</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C58" t="str">
+        <v>https://meli.la/1FpsqGq</v>
+      </c>
+      <c r="D58" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E58" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G58" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_608153-MLB97012029091_112025-V-relogio-masculino-de-pulso-social-classico-casual-original.webp</v>
+      </c>
+      <c r="H58" t="str">
+        <v>R$ 69</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Anel De Prata 925 Claddagh Esmeralda - Exclusivo</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C59" t="str">
+        <v>https://meli.la/2LsMsPz</v>
+      </c>
+      <c r="D59" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E59" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G59" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_673583-MLB50126769271_052022-V-anel-de-prata-925-claddagh-esmeralda-exclusivo.webp</v>
+      </c>
+      <c r="H59" t="str">
+        <v>R$ 147</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Kit 4 Potes Acrílico 3,8l Organizador Geladeira Rebirth</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C60" t="str">
+        <v>https://meli.la/2fyak4n</v>
+      </c>
+      <c r="D60" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E60" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F60" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G60" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_735971-MLA95941810245_102025-V.webp</v>
+      </c>
+      <c r="H60" t="str">
+        <v>R$ 67</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Jogo De Cama Casal Luxo 400 Fios Ponto Palito 3 Peças C/ Fronha Toque Macio Confortável Cor Vermelho Premium Liso</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C61" t="str">
+        <v>https://meli.la/223MzRC</v>
+      </c>
+      <c r="D61" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E61" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F61" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G61" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_965649-MLA99595075122_122025-V.webp</v>
+      </c>
+      <c r="H61" t="str">
+        <v>R$ 29</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Tênis Jada Feminino Puma</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C62" t="str">
+        <v>https://meli.la/12v638s</v>
+      </c>
+      <c r="D62" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E62" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G62" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_706517-MLB82678208779_022025-V-tnis-jada-feminino-puma.webp</v>
+      </c>
+      <c r="H62" t="str">
+        <v>R$ 216</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Nail Drill Bahrein Lixadeira Elétrica Rosa Profissional Para Unhas Gel Fibra Acrílica Acrigel Manicure Pedicure Polimento Motor Portátil Kit Completo Uso Doméstico E Salão 127/220v</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C63" t="str">
+        <v>https://meli.la/2RW6MV8</v>
+      </c>
+      <c r="D63" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E63" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G63" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_600195-MLA109370183193_032026-V.webp</v>
+      </c>
+      <c r="H63" t="str">
+        <v>R$ 22</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Kit 4 Refis De Almofada Laribaby Super Macio Para Enchimento De Fibra Siliconada Antialérgico 45x45 Cm Branco Liso</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C64" t="str">
+        <v>https://meli.la/1kLyBqe</v>
+      </c>
+      <c r="D64" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E64" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G64" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_948486-MLA99596511822_122025-V.webp</v>
+      </c>
+      <c r="H64" t="str">
+        <v>R$ 34</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Cortador Alimentos Ralador Para Cozinha 16 Em 1 Fatiador Verde</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C65" t="str">
+        <v>https://meli.la/1GdYwj6</v>
+      </c>
+      <c r="D65" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E65" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G65" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_825432-MLB109247520924_042026-V.webp</v>
+      </c>
+      <c r="H65" t="str">
+        <v>R$ 36</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Alicate Unha Profissional E Cuticulas Em Aço Inox Cirúrgico Alta Precisão, Corte Afiado, Durável, Uso Manicure E Pedicure Torvstore Prateado</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C66" t="str">
+        <v>https://meli.la/1VJfzY3</v>
+      </c>
+      <c r="D66" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E66" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G66" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_977462-MLA108167552182_032026-V.webp</v>
+      </c>
+      <c r="H66" t="str">
+        <v>R$ 19</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Manta Para Sofá Gigante Decorativa Protetora 2,40x1,80</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C67" t="str">
+        <v>https://meli.la/1t6Nrqh</v>
+      </c>
+      <c r="D67" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E67" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G67" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_677513-MLB50759806799_072022-V-manta-para-sofa-gigante-decorativa-protetora-240x180.webp</v>
+      </c>
+      <c r="H67" t="str">
+        <v>R$ 31</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Celular Samsung Galaxy S25 Fe 5g, 128gb, 8gb Ram, Câmera Tripla De 50+12+8, Tela Grande De 6.7 Azul Marinho</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C68" t="str">
+        <v>https://meli.la/2gr4Lvt</v>
+      </c>
+      <c r="D68" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E68" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G68" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_993303-MLA96666133268_112025-V.webp</v>
+      </c>
+      <c r="H68" t="str">
+        <v>R$ 2.899</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Suporte Aplicador De Fita Adesiva Larga Grande 50mm Com Cortador Dispensador Manual Durex Transparente Fechar Caixas Embalagem Logística Escritório Expedição Pacotes Torvstore Amarelo</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C69" t="str">
+        <v>https://meli.la/22vuP8b</v>
+      </c>
+      <c r="D69" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E69" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G69" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_975933-MLA109366321642_042026-V.webp</v>
+      </c>
+      <c r="H69" t="str">
+        <v>R$ 19</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Kit 4 Telas Mosquiteira Janela Anti-inseto Para Mosquito Proteção Janela Porta Com Velcro Ajustável 130x150 Floresta Urbana Branco</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C70" t="str">
+        <v>https://meli.la/324qrX5</v>
+      </c>
+      <c r="D70" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E70" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G70" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_970666-MLA109027886517_032026-V.webp</v>
+      </c>
+      <c r="H70" t="str">
+        <v>R$ 34</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Bomba Elétrica Filtro Bebedouro De Garrafões Galão D Água Marca: Kamufla Branco</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Oferta Mercado Livre</v>
+      </c>
+      <c r="C71" t="str">
+        <v>https://meli.la/2KkkNRo</v>
+      </c>
+      <c r="D71" t="str">
+        <v>shopping-cart</v>
+      </c>
+      <c r="E71" t="str">
+        <v>#ffe600</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="G71" t="str">
+        <v>https://http2.mlstatic.com/D_Q_NP_2X_828427-MLA99607324950_122025-V.webp</v>
+      </c>
+      <c r="H71" t="str">
+        <v>R$ 19</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H71"/>
   </ignoredErrors>
 </worksheet>
 </file>